--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -17,6 +17,7 @@
     <sheet name="blank_material" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="interierka" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="finishka" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="picturies" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="85">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -216,7 +217,7 @@
     <t xml:space="preserve">Пленка ПЭТ Беклит 215 гр (1,24 м)</t>
   </si>
   <si>
-    <t xml:space="preserve">Холст искуственный Мат; Гл. 260 гр </t>
+    <t xml:space="preserve">Холст искусственный Мат; Гл. 260 гр </t>
   </si>
   <si>
     <t xml:space="preserve">Фотообои </t>
@@ -247,6 +248,42 @@
   </si>
   <si>
     <t xml:space="preserve">Без полей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 20х30 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 30х30 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 30х40 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 40х40 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 40х50 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 40х60 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 50х50 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 50х70 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 60х60 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 60х70 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 60х90 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картина Холст на подрамнике 90х120 см </t>
   </si>
 </sst>
 </file>
@@ -746,6 +783,322 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="61.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>230</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>2350</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>280</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>420</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>490</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>490</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>550</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>345</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>3150</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>670</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -791,11 +791,11 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="61.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -850,7 +850,8 @@
         <v>2050</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>2050</v>
+        <f aca="false">C3*2.5</f>
+        <v>2625</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>150</v>
@@ -1225,7 +1226,7 @@
         <v>2600</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>3000</v>
+        <v>3250</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>150</v>
@@ -1245,7 +1246,7 @@
         <v>3400</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>3700</v>
+        <v>4200</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>150</v>
@@ -1265,7 +1266,7 @@
         <v>4300</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>4500</v>
+        <v>5400</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>150</v>
@@ -1285,7 +1286,7 @@
         <v>4700</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4950</v>
+        <v>6200</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>150</v>
@@ -1305,7 +1306,7 @@
         <v>4650</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5160</v>
+        <v>6450</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>150</v>
@@ -1325,7 +1326,7 @@
         <v>2900</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3200</v>
+        <v>3970</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>150</v>
@@ -1345,7 +1346,7 @@
         <v>790</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>810</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>150</v>
@@ -1365,7 +1366,7 @@
         <v>720</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>150</v>
@@ -1385,7 +1386,7 @@
         <v>2100</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2300</v>
+        <v>2915</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>150</v>
@@ -1405,7 +1406,7 @@
         <v>1300</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1450</v>
+        <v>1815</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>150</v>
@@ -1425,7 +1426,7 @@
         <v>810</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>150</v>
@@ -1445,7 +1446,7 @@
         <v>5500</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>6100</v>
+        <v>7625</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>150</v>
@@ -1465,7 +1466,7 @@
         <v>950</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1060</v>
+        <v>1325</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>150</v>
@@ -1485,7 +1486,7 @@
         <v>1710</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1900</v>
+        <v>2375</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>150</v>
@@ -1505,7 +1506,7 @@
         <v>3750</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4140</v>
+        <v>5175</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>150</v>
@@ -1525,7 +1526,7 @@
         <v>1790</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2000</v>
+        <v>2475</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>150</v>
@@ -1545,7 +1546,7 @@
         <v>2420</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2680</v>
+        <v>3350</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>150</v>
@@ -1736,7 +1737,8 @@
         <v>350</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>400</v>
+        <f aca="false">C2*2.5</f>
+        <v>500</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>72</v>
@@ -1758,7 +1760,7 @@
         <v>440</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>510</v>
+        <v>640</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>72</v>
@@ -1780,7 +1782,7 @@
         <v>470</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>620</v>
+        <v>760</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>72</v>
@@ -1802,7 +1804,7 @@
         <v>280</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>340</v>
+        <v>415</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>72</v>
@@ -1824,7 +1826,7 @@
         <v>425</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>72</v>
@@ -1846,7 +1848,7 @@
         <v>590</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>650</v>
+        <v>1040</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>72</v>
@@ -1868,7 +1870,7 @@
         <v>370</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>490</v>
+        <v>615</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>72</v>
@@ -1890,7 +1892,7 @@
         <v>440</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>650</v>
+        <v>825</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>72</v>
@@ -1912,7 +1914,7 @@
         <v>290</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>390</v>
+        <v>475</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>72</v>
@@ -1934,7 +1936,7 @@
         <v>522</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>580</v>
+        <v>1030</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>72</v>
@@ -1956,7 +1958,7 @@
         <v>280</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>72</v>
@@ -2596,7 +2598,8 @@
         <v>250</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>275</v>
+        <f aca="false">C3*2.5</f>
+        <v>312.5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2613,7 +2616,7 @@
         <v>400</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2630,7 +2633,7 @@
         <v>180</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2647,7 +2650,7 @@
         <v>460</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>460</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2664,7 +2667,7 @@
         <v>220</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2681,7 +2684,7 @@
         <v>300</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>300</v>
+        <v>625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2698,7 +2701,7 @@
         <v>240</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2769,7 +2772,8 @@
         <v>520</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>550</v>
+        <f aca="false">C2*2.5</f>
+        <v>725</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>150</v>
@@ -2789,7 +2793,7 @@
         <v>640</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>150</v>
@@ -2809,7 +2813,7 @@
         <v>1190</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>150</v>
@@ -2829,9 +2833,11 @@
         <v>330</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>420</v>
-      </c>
-      <c r="F5" s="7"/>
+        <v>575</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
@@ -2847,9 +2853,11 @@
         <v>390</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>450</v>
-      </c>
-      <c r="F6" s="7"/>
+        <v>700</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
@@ -2865,9 +2873,11 @@
         <v>530</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>840</v>
-      </c>
-      <c r="F7" s="7"/>
+        <v>1050</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
@@ -2883,7 +2893,7 @@
         <v>580</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>980</v>
+        <v>1225</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>150</v>
@@ -2903,7 +2913,7 @@
         <v>580</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>980</v>
+        <v>1225</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>150</v>
@@ -2923,7 +2933,7 @@
         <v>670</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>900</v>
+        <v>1375</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>150</v>
@@ -2943,7 +2953,7 @@
         <v>460</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>695</v>
+        <v>865</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>150</v>
@@ -2963,7 +2973,7 @@
         <v>765</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>860</v>
+        <v>1125</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>150</v>
@@ -2983,7 +2993,7 @@
         <v>1140</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1300</v>
+        <v>1675</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>150</v>
@@ -3003,7 +3013,7 @@
         <v>1200</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1460</v>
+        <v>1825</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>150</v>
@@ -3023,7 +3033,7 @@
         <v>1060</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1200</v>
+        <v>1475</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>150</v>
@@ -3043,7 +3053,7 @@
         <v>900</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>150</v>
@@ -3063,7 +3073,7 @@
         <v>1100</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>150</v>
@@ -3236,7 +3246,7 @@
         <v>120</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -3259,7 +3269,7 @@
         <v>150</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -3282,7 +3292,7 @@
         <v>150</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -3305,7 +3315,7 @@
         <v>150</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -1737,7 +1737,6 @@
         <v>350</v>
       </c>
       <c r="E2" s="7" t="n">
-        <f aca="false">C2*2.5</f>
         <v>500</v>
       </c>
       <c r="F2" s="7" t="n">

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -2597,8 +2597,7 @@
         <v>250</v>
       </c>
       <c r="E3" s="7" t="n">
-        <f aca="false">C3*2.5</f>
-        <v>312.5</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -850,7 +850,6 @@
         <v>2050</v>
       </c>
       <c r="E3" s="7" t="n">
-        <f aca="false">C3*2.5</f>
         <v>2625</v>
       </c>
       <c r="F3" s="7" t="n">
@@ -2770,7 +2769,6 @@
         <v>520</v>
       </c>
       <c r="E2" s="7" t="n">
-        <f aca="false">C2*2.5</f>
         <v>725</v>
       </c>
       <c r="F2" s="7" t="n">

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="86">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t xml:space="preserve">Люверсы проварка со шнуром</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Люверсы через 30 см в подворот</t>
   </si>
   <si>
     <t xml:space="preserve">Без полей</t>
@@ -404,7 +407,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -463,6 +466,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -821,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>750</v>
@@ -841,7 +848,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1050</v>
@@ -861,7 +868,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1150</v>
@@ -881,7 +888,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>230</v>
@@ -901,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>280</v>
@@ -921,7 +928,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>420</v>
@@ -941,7 +948,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>490</v>
@@ -961,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>490</v>
@@ -981,7 +988,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>550</v>
@@ -1001,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>345</v>
@@ -1021,7 +1028,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1041,7 +1048,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>670</v>
@@ -3322,20 +3329,20 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
+      <c r="C9" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -3345,12 +3352,22 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -18,6 +18,8 @@
     <sheet name="interierka" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="finishka" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="picturies" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="lid_interes" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="lid_status" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="102">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -287,6 +289,54 @@
   </si>
   <si>
     <t xml:space="preserve">Картина Холст на подрамнике 90х120 см </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Печать баннера </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Изготовление таблички</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лазерная резка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стенды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пресс волы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ролл апы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Планы Эвакуации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Печать на холсте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ответил на вопросы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выслал дополнительную информацию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выставил счет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разработка макета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В производстве</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заказ Готов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сообщение о доставке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Просим отзыв о работе</t>
   </si>
 </sst>
 </file>
@@ -407,7 +457,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -466,10 +516,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1106,6 +1152,206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.56"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.92"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -3329,19 +3575,19 @@
       <c r="L8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F9" s="6"/>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -18,8 +18,7 @@
     <sheet name="interierka" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="finishka" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="picturies" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="lid_interes" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="lid_status" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Interest" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -78,9 +77,6 @@
     <t xml:space="preserve">Цена продажи Розница</t>
   </si>
   <si>
-    <t xml:space="preserve">Разрешение печати в DPI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Печать на ПВХ 2 мм</t>
   </si>
   <si>
@@ -291,52 +287,25 @@
     <t xml:space="preserve">Картина Холст на подрамнике 90х120 см </t>
   </si>
   <si>
-    <t xml:space="preserve">Печать баннера </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Изготовление таблички</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лазерная резка</t>
+    <t xml:space="preserve">Интересы</t>
   </si>
   <si>
     <t xml:space="preserve">Стенды</t>
   </si>
   <si>
-    <t xml:space="preserve">Пресс волы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ролл апы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Планы Эвакуации</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Печать на холсте</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ответил на вопросы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выслал дополнительную информацию</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выставил счет</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Разработка макета</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В производстве</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказ Готов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сообщение о доставке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Просим отзыв о работе</t>
+    <t xml:space="preserve">Планы эвакуации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баннера</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ролапы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трафареты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Плоттерная резка</t>
   </si>
 </sst>
 </file>
@@ -841,14 +810,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -865,16 +833,13 @@
       <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>750</v>
@@ -884,9 +849,6 @@
       </c>
       <c r="E2" s="7" t="n">
         <v>1875</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -894,7 +856,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1050</v>
@@ -904,9 +866,6 @@
       </c>
       <c r="E3" s="7" t="n">
         <v>2625</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -914,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1150</v>
@@ -924,9 +883,6 @@
       </c>
       <c r="E4" s="7" t="n">
         <v>2150</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -934,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>230</v>
@@ -944,9 +900,6 @@
       </c>
       <c r="E5" s="7" t="n">
         <v>2350</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -954,7 +907,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>280</v>
@@ -964,9 +917,6 @@
       </c>
       <c r="E6" s="7" t="n">
         <v>2400</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -974,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>420</v>
@@ -984,9 +934,6 @@
       </c>
       <c r="E7" s="7" t="n">
         <v>2500</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -994,7 +941,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>490</v>
@@ -1004,9 +951,6 @@
       </c>
       <c r="E8" s="7" t="n">
         <v>2500</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1014,7 +958,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>490</v>
@@ -1024,9 +968,6 @@
       </c>
       <c r="E9" s="7" t="n">
         <v>2900</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1034,7 +975,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>550</v>
@@ -1044,9 +985,6 @@
       </c>
       <c r="E10" s="7" t="n">
         <v>2900</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1054,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>345</v>
@@ -1064,9 +1002,6 @@
       </c>
       <c r="E11" s="7" t="n">
         <v>3150</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1074,7 +1009,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1084,9 +1019,6 @@
       </c>
       <c r="E12" s="7" t="n">
         <v>3300</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1094,7 +1026,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>670</v>
@@ -1104,9 +1036,6 @@
       </c>
       <c r="E13" s="7" t="n">
         <v>4500</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1115,7 +1044,6 @@
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -1123,7 +1051,6 @@
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
@@ -1131,7 +1058,6 @@
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -1139,7 +1065,6 @@
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1157,188 +1082,63 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.56"/>
-  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.92"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1436,14 +1236,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1460,16 +1260,13 @@
       <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>1300</v>
@@ -1479,9 +1276,6 @@
       </c>
       <c r="E2" s="7" t="n">
         <v>3250</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1489,7 +1283,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1680</v>
@@ -1499,9 +1293,6 @@
       </c>
       <c r="E3" s="7" t="n">
         <v>4200</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,7 +1300,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>2160</v>
@@ -1519,9 +1310,6 @@
       </c>
       <c r="E4" s="7" t="n">
         <v>5400</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1529,7 +1317,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2475</v>
@@ -1539,9 +1327,6 @@
       </c>
       <c r="E5" s="7" t="n">
         <v>6200</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1549,7 +1334,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2580</v>
@@ -1559,9 +1344,6 @@
       </c>
       <c r="E6" s="7" t="n">
         <v>6450</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1569,7 +1351,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1585</v>
@@ -1579,9 +1361,6 @@
       </c>
       <c r="E7" s="7" t="n">
         <v>3970</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1589,7 +1368,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>400</v>
@@ -1599,9 +1378,6 @@
       </c>
       <c r="E8" s="7" t="n">
         <v>1000</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1609,7 +1385,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>450</v>
@@ -1619,9 +1395,6 @@
       </c>
       <c r="E9" s="7" t="n">
         <v>1125</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1629,7 +1402,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>1165</v>
@@ -1639,9 +1412,6 @@
       </c>
       <c r="E10" s="7" t="n">
         <v>2915</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1649,7 +1419,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>725</v>
@@ -1659,9 +1429,6 @@
       </c>
       <c r="E11" s="7" t="n">
         <v>1815</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1669,7 +1436,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1679,9 +1446,6 @@
       </c>
       <c r="E12" s="7" t="n">
         <v>1125</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1689,7 +1453,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>3050</v>
@@ -1699,9 +1463,6 @@
       </c>
       <c r="E13" s="7" t="n">
         <v>7625</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1709,7 +1470,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>530</v>
@@ -1719,9 +1480,6 @@
       </c>
       <c r="E14" s="7" t="n">
         <v>1325</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1729,7 +1487,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>950</v>
@@ -1739,9 +1497,6 @@
       </c>
       <c r="E15" s="7" t="n">
         <v>2375</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1749,7 +1504,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>2070</v>
@@ -1759,9 +1514,6 @@
       </c>
       <c r="E16" s="7" t="n">
         <v>5175</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1769,7 +1521,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>990</v>
@@ -1779,9 +1531,6 @@
       </c>
       <c r="E17" s="7" t="n">
         <v>2475</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1789,7 +1538,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>1340</v>
@@ -1799,9 +1548,6 @@
       </c>
       <c r="E18" s="7" t="n">
         <v>3350</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1810,11 +1556,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1842,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1850,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1858,7 +1600,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1866,7 +1608,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1874,7 +1616,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1901,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1944,7 +1686,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.86"/>
@@ -1952,7 +1694,6 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,18 +1710,15 @@
       <c r="E1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>200</v>
@@ -1991,18 +1729,15 @@
       <c r="E2" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>255</v>
@@ -2013,18 +1748,15 @@
       <c r="E3" s="7" t="n">
         <v>640</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>303</v>
@@ -2035,18 +1767,15 @@
       <c r="E4" s="7" t="n">
         <v>760</v>
       </c>
-      <c r="F4" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>165</v>
@@ -2057,18 +1786,15 @@
       <c r="E5" s="7" t="n">
         <v>415</v>
       </c>
-      <c r="F5" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>250</v>
@@ -2079,18 +1805,15 @@
       <c r="E6" s="7" t="n">
         <v>625</v>
       </c>
-      <c r="F6" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F6" s="6"/>
       <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>415</v>
@@ -2101,18 +1824,15 @@
       <c r="E7" s="7" t="n">
         <v>1040</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>245</v>
@@ -2123,18 +1843,15 @@
       <c r="E8" s="7" t="n">
         <v>615</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>330</v>
@@ -2145,18 +1862,15 @@
       <c r="E9" s="7" t="n">
         <v>825</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>190</v>
@@ -2167,18 +1881,15 @@
       <c r="E10" s="7" t="n">
         <v>475</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>412</v>
@@ -2189,18 +1900,15 @@
       <c r="E11" s="7" t="n">
         <v>1030</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>150</v>
@@ -2211,23 +1919,20 @@
       <c r="E12" s="7" t="n">
         <v>375</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>72</v>
-      </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -2235,9 +1940,8 @@
       <c r="E15" s="7"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
@@ -2245,9 +1949,8 @@
       <c r="E16" s="7"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
@@ -2255,9 +1958,8 @@
       <c r="E17" s="7"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
@@ -2265,9 +1967,8 @@
       <c r="E18" s="7"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
@@ -2275,9 +1976,8 @@
       <c r="E19" s="7"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
@@ -2285,9 +1985,8 @@
       <c r="E20" s="7"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -2295,9 +1994,8 @@
       <c r="E21" s="7"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
@@ -2305,9 +2003,8 @@
       <c r="E22" s="7"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
@@ -2315,9 +2012,8 @@
       <c r="E23" s="7"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -2325,9 +2021,8 @@
       <c r="E24" s="7"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -2335,9 +2030,8 @@
       <c r="E25" s="7"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
@@ -2345,9 +2039,8 @@
       <c r="E26" s="7"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
@@ -2355,9 +2048,8 @@
       <c r="E27" s="7"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -2365,9 +2057,8 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -2375,9 +2066,8 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2385,9 +2075,8 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2395,9 +2084,8 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2405,9 +2093,8 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -2415,9 +2102,8 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -2425,9 +2111,8 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -2435,9 +2120,8 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -2445,9 +2129,8 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -2455,9 +2138,8 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2465,9 +2147,8 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -2475,9 +2156,8 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -2485,9 +2165,8 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2495,9 +2174,8 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2505,9 +2183,8 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2515,9 +2192,8 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2525,9 +2201,8 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2535,9 +2210,8 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-    </row>
-    <row r="46" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -2545,9 +2219,8 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-    </row>
-    <row r="47" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -2555,9 +2228,8 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2565,9 +2237,8 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2575,9 +2246,8 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -2585,9 +2255,8 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2595,9 +2264,8 @@
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-    </row>
-    <row r="52" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -2605,9 +2273,8 @@
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -2615,9 +2282,8 @@
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-    </row>
-    <row r="54" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -2625,9 +2291,8 @@
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -2635,9 +2300,8 @@
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-    </row>
-    <row r="56" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -2645,9 +2309,8 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -2655,9 +2318,8 @@
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -2665,9 +2327,8 @@
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -2675,9 +2336,8 @@
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -2685,9 +2345,8 @@
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2695,9 +2354,8 @@
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2705,9 +2363,8 @@
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2715,9 +2372,8 @@
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2725,9 +2381,8 @@
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -2735,9 +2390,8 @@
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -2745,9 +2399,8 @@
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -2755,9 +2408,8 @@
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -2765,9 +2417,8 @@
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -2775,7 +2426,6 @@
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2823,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>100</v>
@@ -2840,7 +2490,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>125</v>
@@ -2857,7 +2507,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>200</v>
@@ -2874,7 +2524,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>90</v>
@@ -2891,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>230</v>
@@ -2908,7 +2558,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>110</v>
@@ -2925,7 +2575,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>250</v>
@@ -2942,7 +2592,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>120</v>
@@ -2980,14 +2630,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3004,16 +2654,13 @@
       <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>290</v>
@@ -3023,9 +2670,6 @@
       </c>
       <c r="E2" s="7" t="n">
         <v>725</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3033,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>360</v>
@@ -3043,9 +2687,6 @@
       </c>
       <c r="E3" s="7" t="n">
         <v>900</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3053,7 +2694,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>700</v>
@@ -3063,9 +2704,6 @@
       </c>
       <c r="E4" s="7" t="n">
         <v>1750</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3073,7 +2711,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>230</v>
@@ -3083,9 +2721,6 @@
       </c>
       <c r="E5" s="7" t="n">
         <v>575</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,7 +2728,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>280</v>
@@ -3103,9 +2738,6 @@
       </c>
       <c r="E6" s="7" t="n">
         <v>700</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3113,7 +2745,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>420</v>
@@ -3123,9 +2755,6 @@
       </c>
       <c r="E7" s="7" t="n">
         <v>1050</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3133,7 +2762,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>490</v>
@@ -3143,9 +2772,6 @@
       </c>
       <c r="E8" s="7" t="n">
         <v>1225</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3153,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>490</v>
@@ -3163,9 +2789,6 @@
       </c>
       <c r="E9" s="7" t="n">
         <v>1225</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3173,7 +2796,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>550</v>
@@ -3183,9 +2806,6 @@
       </c>
       <c r="E10" s="7" t="n">
         <v>1375</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3193,7 +2813,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>345</v>
@@ -3203,9 +2823,6 @@
       </c>
       <c r="E11" s="7" t="n">
         <v>865</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3213,7 +2830,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -3223,9 +2840,6 @@
       </c>
       <c r="E12" s="7" t="n">
         <v>1125</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3233,7 +2847,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>670</v>
@@ -3243,9 +2857,6 @@
       </c>
       <c r="E13" s="7" t="n">
         <v>1675</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3253,7 +2864,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>730</v>
@@ -3263,9 +2874,6 @@
       </c>
       <c r="E14" s="7" t="n">
         <v>1825</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3273,7 +2881,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>590</v>
@@ -3283,9 +2891,6 @@
       </c>
       <c r="E15" s="7" t="n">
         <v>1475</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3293,7 +2898,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>550</v>
@@ -3303,9 +2908,6 @@
       </c>
       <c r="E16" s="7" t="n">
         <v>1375</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3313,7 +2915,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>520</v>
@@ -3323,9 +2925,6 @@
       </c>
       <c r="E17" s="7" t="n">
         <v>1300</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3349,7 +2948,6 @@
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
@@ -3357,13 +2955,11 @@
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3417,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>0</v>
@@ -3440,7 +3036,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>10</v>
@@ -3463,7 +3059,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>60</v>
@@ -3486,7 +3082,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3509,7 +3105,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>100</v>
@@ -3532,7 +3128,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>100</v>
@@ -3555,7 +3151,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>100</v>
@@ -3579,7 +3175,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>60</v>
@@ -3603,7 +3199,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -1082,7 +1082,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1139,6 +1139,14 @@
       </c>
       <c r="B7" s="3" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="93">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t xml:space="preserve">Без полей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проварка края</t>
   </si>
   <si>
     <t xml:space="preserve">Картина Холст на подрамнике 20х30 см </t>
@@ -740,7 +743,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.57"/>
@@ -811,7 +814,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.31"/>
@@ -839,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>750</v>
@@ -856,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1050</v>
@@ -873,7 +876,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1150</v>
@@ -890,7 +893,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>230</v>
@@ -907,7 +910,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>280</v>
@@ -924,7 +927,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>420</v>
@@ -941,7 +944,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>490</v>
@@ -958,7 +961,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>490</v>
@@ -975,7 +978,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>550</v>
@@ -992,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>345</v>
@@ -1009,7 +1012,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1026,7 +1029,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>670</v>
@@ -1083,14 +1086,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1098,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1106,7 +1109,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1114,7 +1117,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1122,7 +1125,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1130,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1138,15 +1141,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1166,7 +1169,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.57"/>
@@ -1245,7 +1248,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
@@ -1582,7 +1585,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.42"/>
   </cols>
@@ -1644,7 +1647,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
@@ -1695,7 +1698,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G69"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.57"/>
@@ -2452,7 +2455,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.42"/>
@@ -2639,7 +2642,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
@@ -2986,7 +2989,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.29"/>
@@ -3227,11 +3230,21 @@
       <c r="L10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>69</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -206,7 +206,13 @@
     <t xml:space="preserve">Пленка Евро Мат;Гл.;Пр.  80 гр (1,05; 1,27; 1,37; 1,52 м)</t>
   </si>
   <si>
-    <t xml:space="preserve">Пленка Китай Мат;Гл.;Пр.  100 гр (1,05; 1,27; 1,37; 1,52 м)</t>
+    <t xml:space="preserve">Пленка Китай Матовая 100 гр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пленка Китай Глянцевая 100 гр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пленка Китай Прозрачная 100 гр</t>
   </si>
   <si>
     <t xml:space="preserve">Пленка перфорированная (черный оборот) 140 гр (1,37 м)</t>
@@ -842,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>750</v>
@@ -859,7 +865,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1050</v>
@@ -876,7 +882,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1150</v>
@@ -893,7 +899,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>230</v>
@@ -910,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>280</v>
@@ -927,7 +933,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>420</v>
@@ -944,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>490</v>
@@ -961,7 +967,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>490</v>
@@ -978,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>550</v>
@@ -995,7 +1001,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>345</v>
@@ -1012,7 +1018,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1029,7 +1035,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>670</v>
@@ -1093,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1101,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1109,7 +1115,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1117,7 +1123,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1125,7 +1131,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1133,7 +1139,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1141,7 +1147,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1149,7 +1155,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2641,7 +2647,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
@@ -2844,13 +2850,13 @@
         <v>59</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>450</v>
+        <v>345</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>765</v>
+        <v>460</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1125</v>
+        <v>865</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,13 +2867,13 @@
         <v>60</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>670</v>
+        <v>345</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1140</v>
+        <v>460</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1675</v>
+        <v>865</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2875,74 +2881,102 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>730</v>
+        <v>450</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1200</v>
+        <v>765</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1825</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>61</v>
+      <c r="B15" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1060</v>
+        <v>1140</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1475</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>62</v>
+      <c r="B16" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C16" s="7" t="n">
+        <v>730</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>590</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D18" s="7" t="n">
         <v>900</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E18" s="7" t="n">
         <v>1375</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="7" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="7" t="n">
         <v>520</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D19" s="7" t="n">
         <v>1100</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E19" s="7" t="n">
         <v>1300</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
@@ -2955,22 +2989,28 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3024,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>0</v>
@@ -3047,7 +3087,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>10</v>
@@ -3070,7 +3110,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>60</v>
@@ -3093,7 +3133,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3116,7 +3156,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>100</v>
@@ -3139,7 +3179,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>100</v>
@@ -3162,7 +3202,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>100</v>
@@ -3186,7 +3226,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>60</v>
@@ -3210,7 +3250,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -3229,12 +3269,12 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>30</v>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t xml:space="preserve">Плоттерная резка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пресс-вол</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1094,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1156,6 +1159,14 @@
       </c>
       <c r="B8" s="1" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2928,7 +2939,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
@@ -2962,7 +2973,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -1162,10 +1162,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
         <v>350</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -2694,10 +2694,10 @@
         <v>290</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>520</v>
+        <v>340</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>725</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2711,10 +2711,10 @@
         <v>360</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>640</v>
+        <v>420</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>900</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2728,10 +2728,10 @@
         <v>700</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>1190</v>
+        <v>825</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>1750</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2742,13 +2742,13 @@
         <v>52</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D5" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>330</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>575</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2759,10 +2759,10 @@
         <v>53</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>700</v>
@@ -2776,13 +2776,13 @@
         <v>54</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>530</v>
+        <v>495</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1050</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2793,13 +2793,13 @@
         <v>55</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>580</v>
+        <v>475</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1225</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2810,13 +2810,13 @@
         <v>56</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>580</v>
+        <v>475</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1225</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2827,13 +2827,13 @@
         <v>57</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="D10" s="7" t="n">
+        <v>530</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>670</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2844,13 +2844,13 @@
         <v>58</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>460</v>
+        <v>340</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>865</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,13 +2861,13 @@
         <v>59</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>460</v>
+        <v>340</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>865</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2878,13 +2878,13 @@
         <v>60</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>460</v>
+        <v>340</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>865</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2895,13 +2895,13 @@
         <v>61</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>765</v>
+        <v>430</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1125</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2912,13 +2912,13 @@
         <v>62</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>670</v>
+        <v>635</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1140</v>
+        <v>650</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1675</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2935,7 +2935,7 @@
         <v>1200</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1825</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2946,13 +2946,13 @@
         <v>63</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1060</v>
+        <v>560</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1475</v>
+        <v>690</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2969,7 +2969,7 @@
         <v>900</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1375</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2983,10 +2983,10 @@
         <v>520</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1300</v>
+        <v>650</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t xml:space="preserve">Статус продукта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В архиве</t>
   </si>
   <si>
     <t xml:space="preserve">Баннер 440 грамм ламинированный</t>
@@ -851,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>750</v>
@@ -868,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1050</v>
@@ -885,7 +888,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1150</v>
@@ -902,7 +905,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>230</v>
@@ -919,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>280</v>
@@ -936,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>420</v>
@@ -953,7 +956,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>490</v>
@@ -970,7 +973,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>490</v>
@@ -987,7 +990,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>550</v>
@@ -1004,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>345</v>
@@ -1021,7 +1024,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1038,7 +1041,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>670</v>
@@ -1102,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1110,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1118,7 +1121,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1126,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1134,7 +1137,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1142,7 +1145,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1150,7 +1153,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1158,7 +1161,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1166,7 +1169,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1663,7 +1666,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1696,6 +1699,14 @@
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>200</v>
@@ -1784,7 +1795,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>303</v>
@@ -1803,7 +1814,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>165</v>
@@ -1822,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>250</v>
@@ -1841,7 +1852,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>415</v>
@@ -1860,7 +1871,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>245</v>
@@ -1879,7 +1890,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>330</v>
@@ -1898,7 +1909,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>190</v>
@@ -1917,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>412</v>
@@ -1933,10 +1944,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>150</v>
@@ -2501,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>100</v>
@@ -2535,7 +2546,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>200</v>
@@ -2552,7 +2563,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>90</v>
@@ -2569,7 +2580,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>230</v>
@@ -2586,7 +2597,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>110</v>
@@ -2603,7 +2614,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>250</v>
@@ -2620,7 +2631,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>120</v>
@@ -2722,7 +2733,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>700</v>
@@ -2739,7 +2750,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>220</v>
@@ -2756,7 +2767,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>265</v>
@@ -2773,7 +2784,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>400</v>
@@ -2790,7 +2801,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>465</v>
@@ -2807,7 +2818,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>465</v>
@@ -2824,7 +2835,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>520</v>
@@ -2841,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>340</v>
@@ -2858,7 +2869,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>340</v>
@@ -2875,7 +2886,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>340</v>
@@ -2892,7 +2903,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>430</v>
@@ -2909,7 +2920,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>635</v>
@@ -2943,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>560</v>
@@ -2960,7 +2971,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>550</v>
@@ -2977,7 +2988,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>520</v>
@@ -3075,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>0</v>
@@ -3098,7 +3109,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>10</v>
@@ -3121,7 +3132,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>60</v>
@@ -3144,7 +3155,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3167,7 +3178,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>100</v>
@@ -3190,7 +3201,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>100</v>
@@ -3213,7 +3224,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>100</v>
@@ -3237,7 +3248,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>60</v>
@@ -3261,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -3285,7 +3296,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>30</v>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -155,31 +155,31 @@
     <t xml:space="preserve">Баннер 510 грамм литой BlackBack (Черный оборот)</t>
   </si>
   <si>
+    <t xml:space="preserve">Баннерная сетка 370 грамм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пленка самокл-ся Европа мат; гл 80 грамм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пленка самокл-ся Китай мат; гл 80 грамм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пленка перфорированная</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бумага 150 грамм СytiLight </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скройлерная бумага 170 грамм 1,27 м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11э</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Блюбек</t>
+  </si>
+  <si>
     <t xml:space="preserve">Баннер 340 грамм ламинированный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баннерная сетка 370 грамм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пленка самокл-ся Европа мат; гл 80 грамм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пленка самокл-ся Китай мат; гл 80 грамм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пленка перфорированная</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бумага 150 грамм СytiLight </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Скройлерная бумага 170 грамм 1,27 м</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11э</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Блюбек</t>
   </si>
   <si>
     <t xml:space="preserve">Баннер 510 грамм литой (Черный оборот)</t>
@@ -1702,10 +1702,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1725,10 +1725,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.14"/>
@@ -1811,153 +1811,139 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>280</v>
+        <v>425</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>415</v>
+        <v>625</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>250</v>
+        <v>415</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>425</v>
+        <v>590</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>625</v>
+        <v>1040</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>415</v>
+        <v>245</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>590</v>
+        <v>370</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1040</v>
+        <v>615</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>245</v>
+        <v>330</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>370</v>
+        <v>440</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>615</v>
+        <v>825</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>440</v>
+        <v>290</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>825</v>
+        <v>475</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>190</v>
+        <v>412</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>290</v>
+        <v>522</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>475</v>
+        <v>1030</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>10</v>
+      <c r="A11" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>412</v>
+        <v>150</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>522</v>
+        <v>280</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1030</v>
+        <v>375</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>280</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>375</v>
-      </c>
+      <c r="A12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
     </row>
@@ -1968,6 +1954,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
     </row>
@@ -2017,11 +2007,21 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="A20" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>280</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>415</v>
+      </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
     </row>
@@ -2082,9 +2082,9 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
     </row>
@@ -2457,15 +2457,7 @@
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -2563,7 +2555,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>90</v>
@@ -2597,7 +2589,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>110</v>
@@ -2614,7 +2606,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>250</v>
@@ -2631,7 +2623,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>120</v>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t xml:space="preserve">Скройлерная бумага 170 грамм 1,27 м</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11э</t>
   </si>
   <si>
     <t xml:space="preserve">Блюбек</t>
@@ -854,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>750</v>
@@ -871,7 +868,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1050</v>
@@ -888,7 +885,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1150</v>
@@ -905,7 +902,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>230</v>
@@ -922,7 +919,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>280</v>
@@ -939,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>420</v>
@@ -956,7 +953,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>490</v>
@@ -973,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>490</v>
@@ -990,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>550</v>
@@ -1007,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>345</v>
@@ -1024,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1041,7 +1038,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>670</v>
@@ -1105,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1113,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1121,7 +1118,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1129,7 +1126,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1137,7 +1134,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1145,7 +1142,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1153,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1161,7 +1158,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1169,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1924,11 +1921,11 @@
       <c r="G10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>150</v>
@@ -2011,7 +2008,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>165</v>
@@ -2538,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>200</v>
@@ -2555,7 +2552,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>90</v>
@@ -2572,7 +2569,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>230</v>
@@ -2589,7 +2586,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>110</v>
@@ -2725,7 +2722,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>700</v>
@@ -2742,7 +2739,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>220</v>
@@ -2759,7 +2756,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>265</v>
@@ -2776,7 +2773,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>400</v>
@@ -2793,7 +2790,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>465</v>
@@ -2810,7 +2807,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>465</v>
@@ -2827,7 +2824,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>520</v>
@@ -2844,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>340</v>
@@ -2861,7 +2858,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>340</v>
@@ -2878,7 +2875,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>340</v>
@@ -2895,7 +2892,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>430</v>
@@ -2912,7 +2909,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>635</v>
@@ -2946,7 +2943,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>560</v>
@@ -2963,7 +2960,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>550</v>
@@ -2980,7 +2977,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>520</v>
@@ -3078,7 +3075,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>0</v>
@@ -3101,7 +3098,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>10</v>
@@ -3124,7 +3121,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>60</v>
@@ -3147,7 +3144,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3170,7 +3167,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>100</v>
@@ -3193,7 +3190,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>100</v>
@@ -3216,7 +3213,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>100</v>
@@ -3240,7 +3237,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>60</v>
@@ -3264,7 +3261,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -3288,7 +3285,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>30</v>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -317,7 +317,13 @@
     <t xml:space="preserve">Плоттерная резка</t>
   </si>
   <si>
+    <t xml:space="preserve">Наклейки</t>
+  </si>
+  <si>
     <t xml:space="preserve">Пресс-вол</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблички</t>
   </si>
 </sst>
 </file>
@@ -1094,8 +1100,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.59"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
@@ -1158,7 +1167,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1166,7 +1175,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/files/management/commands/price.xlsx
+++ b/files/management/commands/price.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="delivery" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="status_order" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="uf-print" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="type_print" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="status_product" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="shirka" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="blank_material" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="interierka" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="finishka" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="picturies" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Interest" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="status_order" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="uf-print" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="type_print" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="status_product" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="shirka" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="blank_material" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="interierka" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="finishka" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="picturies" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Interest" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,18 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="95">
   <si>
     <t xml:space="preserve">№</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Типы доставки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Самовывоз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автобусом по М4 (в сторону Москвы)</t>
   </si>
   <si>
     <t xml:space="preserve">Статус Заказа</t>
@@ -792,25 +782,33 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -828,282 +826,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.45"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>750</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>1750</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>2050</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>2625</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>1150</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>2150</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>230</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>2350</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>2350</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>280</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>420</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>490</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>490</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>2900</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>550</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>2900</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>345</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>3150</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>450</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>3300</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>670</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1119,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1127,7 +853,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1135,7 +861,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,7 +869,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1151,7 +877,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1159,7 +885,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1167,7 +893,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1175,15 +901,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>97</v>
+      <c r="B10" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1198,85 +924,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.57"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1294,16 +941,16 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1311,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>1300</v>
@@ -1328,7 +975,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1680</v>
@@ -1345,7 +992,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>2160</v>
@@ -1362,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2475</v>
@@ -1379,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2580</v>
@@ -1396,7 +1043,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1585</v>
@@ -1413,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>400</v>
@@ -1430,7 +1077,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>450</v>
@@ -1447,7 +1094,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>1165</v>
@@ -1464,7 +1111,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>725</v>
@@ -1481,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>450</v>
@@ -1498,7 +1145,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>3050</v>
@@ -1515,7 +1162,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>530</v>
@@ -1532,7 +1179,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>950</v>
@@ -1549,7 +1196,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>2070</v>
@@ -1566,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>990</v>
@@ -1583,7 +1230,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>1340</v>
@@ -1601,6 +1248,68 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.42"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1620,16 +1329,13 @@
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.42"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1637,7 +1343,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1645,7 +1351,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1653,15 +1359,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>36</v>
+      <c r="B5" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1676,65 +1382,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1752,16 +1399,16 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6"/>
       <c r="B1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>14</v>
       </c>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -1771,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>200</v>
@@ -1790,7 +1437,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>255</v>
@@ -1809,7 +1456,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>303</v>
@@ -1828,7 +1475,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>250</v>
@@ -1847,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>415</v>
@@ -1866,7 +1513,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>245</v>
@@ -1885,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>330</v>
@@ -1904,7 +1551,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>190</v>
@@ -1923,7 +1570,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>412</v>
@@ -1942,7 +1589,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>150</v>
@@ -2025,7 +1672,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>165</v>
@@ -2483,7 +2130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2501,16 +2148,16 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6"/>
       <c r="B1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2518,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>100</v>
@@ -2535,7 +2182,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>125</v>
@@ -2552,7 +2199,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>200</v>
@@ -2569,7 +2216,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>90</v>
@@ -2586,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>230</v>
@@ -2603,7 +2250,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>110</v>
@@ -2620,7 +2267,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>250</v>
@@ -2637,7 +2284,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>120</v>
@@ -2670,7 +2317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2688,16 +2335,16 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2705,16 +2352,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>290</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2722,16 +2369,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>360</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>490</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2739,7 +2386,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>700</v>
@@ -2756,7 +2403,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>220</v>
@@ -2773,7 +2420,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>265</v>
@@ -2782,7 +2429,7 @@
         <v>330</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>700</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2790,7 +2437,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>400</v>
@@ -2807,7 +2454,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>465</v>
@@ -2824,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>465</v>
@@ -2841,7 +2488,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>520</v>
@@ -2858,7 +2505,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>340</v>
@@ -2875,7 +2522,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>340</v>
@@ -2892,7 +2539,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>340</v>
@@ -2909,7 +2556,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>430</v>
@@ -2926,7 +2573,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>635</v>
@@ -2943,7 +2590,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>730</v>
@@ -2960,7 +2607,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>560</v>
@@ -2977,7 +2624,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>550</v>
@@ -2994,7 +2641,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>520</v>
@@ -3051,7 +2698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3069,16 +2716,16 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6"/>
       <c r="B1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>14</v>
       </c>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -3092,7 +2739,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>0</v>
@@ -3115,7 +2762,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>10</v>
@@ -3138,7 +2785,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>60</v>
@@ -3161,7 +2808,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>80</v>
@@ -3184,7 +2831,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>100</v>
@@ -3207,7 +2854,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>100</v>
@@ -3230,7 +2877,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>100</v>
@@ -3254,7 +2901,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>60</v>
@@ -3278,7 +2925,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -3302,7 +2949,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>30</v>
@@ -3778,4 +3425,276 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.45"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>230</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>2350</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>280</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>420</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>490</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>490</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>550</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>345</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>3150</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>670</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>